--- a/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="216" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A630EA59-3DC7-4213-B2DC-6040A3DC4258}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{087F7AC9-EE55-4C9C-B047-4C87CC010C56}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>Project ID</t>
   </si>
@@ -116,6 +117,12 @@
     <t>Accelerating just energy transition</t>
   </si>
   <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t>Number of students benefitted</t>
+  </si>
+  <si>
     <t>Water Services</t>
   </si>
   <si>
@@ -156,6 +163,9 @@
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves</t>
+  </si>
+  <si>
+    <t>10600 HH</t>
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves is 10,600 people
@@ -175,10 +185,10 @@
 Solarization of national warehouse for medicines and medical equipment (SAMES) and 2 community health centers. Estimated beneficiaries (650,000 people)</t>
   </si>
   <si>
+    <t>h</t>
+  </si>
+  <si>
     <t>Renewable Energy</t>
-  </si>
-  <si>
-    <t>Education Services</t>
   </si>
   <si>
     <t>Solarization of ICT labs in 15 public secondary/vocation schools with estimated beneficiaries (18,060 people)</t>
@@ -567,7 +577,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -634,6 +644,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -660,75 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1034,15 +1050,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09FFFD-BF9A-4603-B1BD-9865A24B4529}">
-  <dimension ref="A1:S7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F479CD-277A-444C-9A31-93368D511EC2}">
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="10" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="8" width="12.7109375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" customWidth="1"/>
+    <col min="9" max="9" width="65.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.28515625" customWidth="1"/>
     <col min="13" max="13" width="62" style="6" customWidth="1"/>
     <col min="15" max="15" width="11.5703125" customWidth="1"/>
@@ -1052,75 +1068,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="47.25" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="S1" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A2" s="48">
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="45.75">
+      <c r="A2" s="39">
         <v>126532</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="37">
         <v>2700742</v>
       </c>
       <c r="E2" s="19" t="s">
@@ -1141,7 +1157,7 @@
       <c r="J2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="33">
+      <c r="K2" s="24">
         <v>0.47</v>
       </c>
       <c r="L2" s="21"/>
@@ -1157,13 +1173,11 @@
       <c r="R2" s="21"/>
       <c r="S2" s="21"/>
     </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="60.75">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="46">
-        <v>2700742</v>
-      </c>
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="30.75">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="19" t="s">
         <v>27</v>
       </c>
@@ -1171,11 +1185,395 @@
         <v>28</v>
       </c>
       <c r="G3" s="20"/>
+      <c r="H3" s="20">
+        <v>1712</v>
+      </c>
+      <c r="I3" s="19"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+    </row>
+    <row r="4" spans="1:19" s="6" customFormat="1" ht="60.75">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+    </row>
+    <row r="5" spans="1:19" s="6" customFormat="1" ht="78" customHeight="1">
+      <c r="A5" s="35">
+        <v>145070</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="18">
+        <v>129875</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <v>100</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="22">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+    </row>
+    <row r="6" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1">
+      <c r="A6" s="44">
+        <v>1000417</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="37">
+        <v>700000</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="32"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+    </row>
+    <row r="7" spans="1:19" s="6" customFormat="1" ht="121.5">
+      <c r="A7" s="45"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="37">
+        <v>1000000</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21">
+        <v>650000</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+    </row>
+    <row r="8" spans="1:19" s="6" customFormat="1" ht="91.5">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37">
+        <v>2000000</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="21">
+        <v>18060</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="36"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{386D73ED-6A41-4443-91ED-8CD70BAAD633}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{7A5099D1-2ED5-43E4-AD13-261638184DF9}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{1B26F938-4EBD-46CC-831A-597505A8B9BC}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P8" xr:uid="{5BEEAE34-0BCA-4954-A953-F33D3CEC6CD0}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{E8931478-6827-48AC-B5DC-292C1313AC0D}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{779FF747-E687-4012-AE8E-69AFE9D31B33}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{33F8B1CB-D415-4A02-B636-DAE94AE482E9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F1CF943B-2F7C-4B2D-B1D7-BC5BF3B5A006}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09FFFD-BF9A-4603-B1BD-9865A24B4529}">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="10" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="65.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="62" style="6" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="47.25" customHeight="1">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="91.5">
+      <c r="A2" s="39">
+        <v>126532</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="37">
+        <v>2700742</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="20">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="24">
+        <v>0.47</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+    </row>
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="60.75">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="20"/>
       <c r="H3" s="20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>25</v>
@@ -1188,30 +1586,30 @@
         <v>26</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
     </row>
     <row r="4" spans="1:19" s="6" customFormat="1" ht="78" customHeight="1">
-      <c r="A4" s="44">
+      <c r="A4" s="35">
         <v>145070</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>33</v>
+      <c r="B4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="D4" s="18">
         <v>129875</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="18">
         <v>0</v>
@@ -1220,16 +1618,16 @@
         <v>100</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>39</v>
       </c>
       <c r="K4" s="22">
         <v>1</v>
       </c>
       <c r="L4" s="21"/>
-      <c r="M4" s="34"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="21"/>
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
@@ -1238,35 +1636,35 @@
       <c r="S4" s="21"/>
     </row>
     <row r="5" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="53">
+      <c r="A5" s="44">
         <v>1000417</v>
       </c>
-      <c r="B5" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="46">
+      <c r="B5" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="37">
         <v>700000</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="G5" s="18">
         <v>0</v>
       </c>
-      <c r="H5" s="18">
-        <v>10600</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="41"/>
+      <c r="H5" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="32"/>
       <c r="L5" s="23"/>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
@@ -1274,24 +1672,24 @@
         <v>26</v>
       </c>
       <c r="P5" s="21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q5" s="21"/>
       <c r="R5" s="21"/>
       <c r="S5" s="21"/>
     </row>
     <row r="6" spans="1:19" s="6" customFormat="1" ht="137.25">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="46">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="37">
         <v>1000000</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -1299,11 +1697,11 @@
       <c r="H6" s="21">
         <v>650000</v>
       </c>
-      <c r="I6" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="41"/>
+      <c r="I6" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="35"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="23"/>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
@@ -1311,34 +1709,34 @@
         <v>26</v>
       </c>
       <c r="P6" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="21"/>
       <c r="R6" s="21"/>
       <c r="S6" s="21"/>
     </row>
     <row r="7" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37">
         <v>2000000</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>48</v>
+        <v>27</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>51</v>
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="21">
         <v>18060</v>
       </c>
-      <c r="I7" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="41"/>
+      <c r="I7" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="36"/>
+      <c r="K7" s="32"/>
       <c r="L7" s="23"/>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -1346,7 +1744,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="21"/>
       <c r="R7" s="21"/>
@@ -1390,7 +1788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1439,13 +1837,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="91.5">
-      <c r="A2" s="26">
+      <c r="A2" s="51">
         <v>126532</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="52" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="9">
@@ -1470,34 +1868,34 @@
         <v>25</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60.75">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="28"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="9">
         <v>2700742</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15">
         <v>600</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51" customHeight="1">
@@ -1505,10 +1903,10 @@
         <v>145070</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="9">
         <v>129875</v>
@@ -1517,32 +1915,32 @@
         <v>21</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="15">
         <v>0</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="24">
+      <c r="A5" s="49">
         <v>1000417</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="25"/>
+      <c r="B5" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="50"/>
       <c r="D5" s="9">
         <v>700000</v>
       </c>
@@ -1550,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
@@ -1559,24 +1957,24 @@
         <v>1000</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>42</v>
+        <v>56</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="91.5">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="9">
         <v>1000000</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -1585,22 +1983,22 @@
         <v>3</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="24"/>
+        <v>58</v>
+      </c>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:11" ht="60.75">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="10">
         <v>2000000</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="10">
         <v>3</v>
@@ -1609,9 +2007,9 @@
         <v>15</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="24"/>
+        <v>60</v>
+      </c>
+      <c r="J7" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1643,7 +2041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1653,160 +2051,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="29" t="s">
-        <v>60</v>
+      <c r="A2" s="54" t="s">
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="29"/>
+      <c r="A3" s="54"/>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="29"/>
+      <c r="A4" s="54"/>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="30" t="s">
-        <v>65</v>
+      <c r="A5" s="55" t="s">
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="30"/>
+      <c r="A6" s="55"/>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="30"/>
+      <c r="A7" s="55"/>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="55"/>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="30"/>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="30"/>
+      <c r="A9" s="55"/>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="31" t="s">
-        <v>73</v>
+      <c r="A10" s="56" t="s">
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="31"/>
+      <c r="A11" s="56"/>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="32" t="s">
-        <v>77</v>
+      <c r="A12" s="57" t="s">
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="32"/>
+      <c r="A13" s="57"/>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="32"/>
+      <c r="A14" s="57"/>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1821,15 +2219,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2078,6 +2467,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2090,11 +2488,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C7E208-C61E-4AAF-AAB6-F295214DA82E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C7E208-C61E-4AAF-AAB6-F295214DA82E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27307"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{087F7AC9-EE55-4C9C-B047-4C87CC010C56}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98F6E697-7AD7-4D8F-885B-D715D934C598}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
   <si>
     <t>Project ID</t>
   </si>
@@ -69,10 +69,7 @@
     <t>Gender (% female)</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments </t>
+    <t>VF or Non-VF</t>
   </si>
   <si>
     <t>Tag</t>
@@ -93,30 +90,48 @@
     <t>Indirect Taxonomy</t>
   </si>
   <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
+  </si>
+  <si>
     <t>The ACCESS project</t>
   </si>
   <si>
     <t>http://open.undp.org/projects/00126532</t>
   </si>
   <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of rural HH accessed to solar lightings</t>
+  </si>
+  <si>
+    <t>1000 HH</t>
+  </si>
+  <si>
+    <t>Total number of people benefitted from this project is 5,341 people (female: 2,511 and male: 2,830). In addition number of students benefitted from the project (1,712 people)</t>
+  </si>
+  <si>
+    <t>KOICA</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
     <t>Electricity Access</t>
   </si>
   <si>
-    <t>Number of rural HH accessed to solar lightings</t>
-  </si>
-  <si>
-    <t>1000 HH</t>
-  </si>
-  <si>
-    <t>Total number of people benefitted from this project is 5,341 people (female: 2,511 and male: 2,830). In addition number of students benefitted from the project (1,712 people)</t>
-  </si>
-  <si>
-    <t>KOICA</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
     <t>Education Services</t>
   </si>
   <si>
@@ -163,9 +178,6 @@
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves</t>
-  </si>
-  <si>
-    <t>10600 HH</t>
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves is 10,600 people
@@ -185,9 +197,6 @@
 Solarization of national warehouse for medicines and medical equipment (SAMES) and 2 community health centers. Estimated beneficiaries (650,000 people)</t>
   </si>
   <si>
-    <t>h</t>
-  </si>
-  <si>
     <t>Renewable Energy</t>
   </si>
   <si>
@@ -198,6 +207,15 @@
 3 ICT schools solarized  </t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments </t>
+  </si>
+  <si>
+    <t>10600 HH</t>
+  </si>
+  <si>
     <t>Can you provide information on this project?  Please note that the target number should reflect an estimate of the number of beneficiaries reached by the project. Details can be explained in the note</t>
   </si>
   <si>
@@ -222,43 +240,52 @@
     <t xml:space="preserve">Solarization of ICT labs in 15 public secondary/vocation schools with estimated beneficiaries (18,060 people) </t>
   </si>
   <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Access to Energy</t>
-  </si>
-  <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
   </si>
   <si>
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
-  </si>
-  <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Access to agricultural energy services (irrigation with solar pumps, heating systems for processing food, etc. )</t>
-  </si>
-  <si>
-    <t>Access to health services powered by solar PV and energy efficient systems such as hospitals</t>
-  </si>
-  <si>
-    <t>Access to solar water pumps</t>
-  </si>
-  <si>
-    <t>Access to education services trough clean energy systems</t>
+    <t>Number of MW installed capacity</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -267,7 +294,10 @@
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t>Market Development</t>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Medium Enterprises</t>
@@ -279,13 +309,10 @@
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t>Individuals who participate in trainings for energy activities</t>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
   </si>
   <si>
     <t>Entrepreneurship Training</t>
@@ -294,19 +321,19 @@
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
   </si>
   <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
     <t>Campaign Participant</t>
   </si>
   <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
   </si>
   <si>
-    <t>Policy and Regulator Frameworks</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
-    <t>Policies and regulatory framework can have far-reaching impacts on the energy access situation in countries</t>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
   </si>
   <si>
     <t>Other</t>
@@ -322,12 +349,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -364,8 +397,21 @@
       <name val="Helvetica Neue"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,42 +421,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE497"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FFFFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42FFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00E1DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BDB7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,23 +582,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -597,154 +601,176 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1051,366 +1077,446 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F479CD-277A-444C-9A31-93368D511EC2}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" style="10" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="8" customWidth="1"/>
     <col min="9" max="9" width="65.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="62" style="6" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="11.85546875" customWidth="1"/>
-    <col min="19" max="19" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="47.25" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:25" ht="47.25" customHeight="1">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="53" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="45.75">
-      <c r="A2" s="39">
+      <c r="T1" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="4" customFormat="1" ht="60.75">
+      <c r="A2" s="37">
         <v>126532</v>
       </c>
-      <c r="B2" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="37">
+      <c r="B2" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="35">
         <v>2700742</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="20">
+      <c r="E2" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="18">
         <v>0</v>
       </c>
-      <c r="H2" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="24">
+      <c r="I2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="22">
         <v>0.47</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-    </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="30.75">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="19" t="s">
+      <c r="L2" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="47"/>
+      <c r="N2" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="55"/>
+      <c r="X2" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="4" customFormat="1" ht="45.75">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18">
+        <v>1712</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="47"/>
+      <c r="N3" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="55"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+    </row>
+    <row r="4" spans="1:25" s="4" customFormat="1" ht="60.75">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="K4" s="19"/>
+      <c r="L4" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20">
-        <v>1712</v>
-      </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-    </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="60.75">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="19" t="s">
+      <c r="M4" s="47"/>
+      <c r="N4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="55"/>
+      <c r="X4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="19" t="s">
+      <c r="Y4" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="4" customFormat="1" ht="78" customHeight="1">
+      <c r="A5" s="33">
+        <v>145070</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="16">
+        <v>129875</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <v>100</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="20">
+        <v>1</v>
+      </c>
+      <c r="L5" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="47"/>
+      <c r="N5" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="55"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+    </row>
+    <row r="6" spans="1:25" s="4" customFormat="1" ht="60.75">
+      <c r="A6" s="42">
+        <v>1000417</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="35">
+        <v>700000</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <v>10600</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="47"/>
+      <c r="N6" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="55"/>
+      <c r="X6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="4" customFormat="1" ht="121.5">
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="35">
+        <v>1000000</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
+        <v>650000</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="47"/>
+      <c r="N7" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="55"/>
+      <c r="X7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" s="4" customFormat="1" ht="91.5">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="35">
+        <v>2000000</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-    </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="78" customHeight="1">
-      <c r="A5" s="35">
-        <v>145070</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="18">
-        <v>129875</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="18">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18">
-        <v>100</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="22">
-        <v>1</v>
-      </c>
-      <c r="L5" s="21"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-    </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1">
-      <c r="A6" s="44">
-        <v>1000417</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="37">
-        <v>700000</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="32"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-    </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" ht="121.5">
-      <c r="A7" s="45"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="37">
-        <v>1000000</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="18">
-        <v>0</v>
-      </c>
-      <c r="H7" s="21">
-        <v>650000</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-    </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37">
-        <v>2000000</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="21">
+      <c r="F8" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="19">
         <v>18060</v>
       </c>
-      <c r="I8" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
+      <c r="I8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="47"/>
+      <c r="N8" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="55"/>
+      <c r="X8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y8" s="19" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{386D73ED-6A41-4443-91ED-8CD70BAAD633}">
-      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{7A5099D1-2ED5-43E4-AD13-261638184DF9}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{7A5099D1-2ED5-43E4-AD13-261638184DF9}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{1B26F938-4EBD-46CC-831A-597505A8B9BC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P8" xr:uid="{1B26F938-4EBD-46CC-831A-597505A8B9BC}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P8" xr:uid="{5BEEAE34-0BCA-4954-A953-F33D3CEC6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y8" xr:uid="{5BEEAE34-0BCA-4954-A953-F33D3CEC6CD0}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{E8931478-6827-48AC-B5DC-292C1313AC0D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X8 N2:N8" xr:uid="{E8931478-6827-48AC-B5DC-292C1313AC0D}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{BECE492C-710C-49E8-9E3C-10BDCAD51DB5}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M8" xr:uid="{03EC0A59-33AD-4A38-A59F-5790EAF0FE95}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T8" xr:uid="{E80C4C84-0BAE-4A42-B940-7C66CD6D2919}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L8" xr:uid="{62EDF95F-C0FC-4DE6-AE3F-F2141A9A12CD}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{5D645D24-9CBD-4A5E-8BAB-AE797F3CDCCF}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{D9460CF6-46EF-49D0-9567-3BA1F1DCC2EA}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -1420,12 +1526,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F1CF943B-2F7C-4B2D-B1D7-BC5BF3B5A006}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E9</xm:sqref>
+          <xm:sqref>E9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4067C5F9-0F49-483B-A43E-91951C4F55C6}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1439,12 +1551,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" style="10" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="8" customWidth="1"/>
     <col min="9" max="9" width="65.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="62" style="6" customWidth="1"/>
+    <col min="13" max="13" width="62" style="4" customWidth="1"/>
     <col min="15" max="15" width="11.5703125" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" customWidth="1"/>
     <col min="18" max="18" width="11.85546875" customWidth="1"/>
@@ -1452,303 +1564,303 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="47.25" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="30" t="s">
+      <c r="L1" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="O1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="P1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="Q1" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="R1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="S1" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A2" s="39">
+    </row>
+    <row r="2" spans="1:19" s="4" customFormat="1" ht="91.5">
+      <c r="A2" s="37">
         <v>126532</v>
       </c>
-      <c r="B2" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="37">
+      <c r="B2" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="35">
         <v>2700742</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="20">
+      <c r="E2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="18">
         <v>0</v>
       </c>
-      <c r="H2" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="24">
+      <c r="I2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="22">
         <v>0.47</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-    </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="60.75">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="19" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20" t="s">
+      <c r="P2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+    </row>
+    <row r="3" spans="1:19" s="4" customFormat="1" ht="60.75">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+    </row>
+    <row r="4" spans="1:19" s="4" customFormat="1" ht="78" customHeight="1">
+      <c r="A4" s="33">
+        <v>145070</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="16">
+        <v>129875</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16">
+        <v>100</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="20">
+        <v>1</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+    </row>
+    <row r="5" spans="1:19" s="4" customFormat="1" ht="30" customHeight="1">
+      <c r="A5" s="42">
+        <v>1000417</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="35">
+        <v>700000</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="30"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+    </row>
+    <row r="6" spans="1:19" s="4" customFormat="1" ht="137.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="35">
+        <v>1000000</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>650000</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="33"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+    </row>
+    <row r="7" spans="1:19" s="4" customFormat="1" ht="91.5">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="35">
+        <v>2000000</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-    </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="78" customHeight="1">
-      <c r="A4" s="35">
-        <v>145070</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="18">
-        <v>129875</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="18">
-        <v>0</v>
-      </c>
-      <c r="H4" s="18">
-        <v>100</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="22">
-        <v>1</v>
-      </c>
-      <c r="L4" s="21"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-    </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="44">
-        <v>1000417</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="37">
-        <v>700000</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="18">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-    </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" ht="137.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="37">
-        <v>1000000</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>650000</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="35"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-    </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" ht="91.5">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37">
-        <v>2000000</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="21">
+      <c r="F7" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="19">
         <v>18060</v>
       </c>
-      <c r="I7" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
+      <c r="I7" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="34"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1778,7 +1890,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA4B507B-7600-43C0-8070-011EA46FA396}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
@@ -1794,11 +1906,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" style="10" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="8" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" customWidth="1"/>
-    <col min="11" max="11" width="62" style="6" customWidth="1"/>
+    <col min="11" max="11" width="62" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1811,7 +1923,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1820,196 +1932,196 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>12</v>
+      <c r="K1" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="91.5">
-      <c r="A2" s="51">
+      <c r="A2" s="58">
         <v>126532</v>
       </c>
-      <c r="B2" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="9">
+      <c r="B2" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="7">
         <v>2700742</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="15">
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="13">
         <v>0</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="13">
         <v>1000</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>24</v>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60.75">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="9">
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="7">
         <v>2700742</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15">
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13">
         <v>600</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="51" customHeight="1">
+      <c r="A4" s="14">
+        <v>145070</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7">
+        <v>129875</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1">
+      <c r="A5" s="56">
+        <v>1000417</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="7">
+        <v>700000</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="91.5">
+      <c r="A6" s="56"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="56"/>
+    </row>
+    <row r="7" spans="1:11" ht="60.75">
+      <c r="A7" s="56"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="51" customHeight="1">
-      <c r="A4" s="16">
-        <v>145070</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="9">
-        <v>129875</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="49">
-        <v>1000417</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="9">
-        <v>700000</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="49" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="91.5">
-      <c r="A6" s="49"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="9">
-        <v>1000000</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="F7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="8">
         <v>3</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="49"/>
-    </row>
-    <row r="7" spans="1:11" ht="60.75">
-      <c r="A7" s="49"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="10">
-        <v>3</v>
-      </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>15</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="49"/>
+      <c r="I7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2031,7 +2143,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
@@ -2043,182 +2155,214 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="52.7109375" customWidth="1"/>
+    <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="54"/>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="54"/>
-      <c r="B4" t="s">
+      <c r="B1" s="48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="45.75">
+      <c r="A2" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="62" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="55"/>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="55"/>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="55"/>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="55"/>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="56"/>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="57"/>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="57"/>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" s="62" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" s="49" t="s">
         <v>91</v>
       </c>
     </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="62" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="62" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="62" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2467,34 +2611,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C7E208-C61E-4AAF-AAB6-F295214DA82E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA980070-F43E-4A4D-AE3A-45EBDF1E7F16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA980070-F43E-4A4D-AE3A-45EBDF1E7F16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C7E208-C61E-4AAF-AAB6-F295214DA82E}"/>
 </file>
--- a/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27307"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="264" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98F6E697-7AD7-4D8F-885B-D715D934C598}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="528" documentId="11_6A2C6EB666106EDC3B71E986BCBC267D10A82215" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27A6C663-FB6B-4FA6-B310-626FE8B99BD3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="124">
   <si>
     <t>Project ID</t>
   </si>
@@ -75,75 +80,187 @@
     <t>Tag</t>
   </si>
   <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>RISE Taxonomy</t>
+  </si>
+  <si>
+    <t>Flagship</t>
+  </si>
+  <si>
+    <t>Indirect Category</t>
+  </si>
+  <si>
+    <t>Indirect Taxonomy</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
+  </si>
+  <si>
+    <t>The ACCESS project</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00126532</t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of rural HH accessed to solar lightings </t>
+  </si>
+  <si>
+    <t>1000 HH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The total number of households (HH) who benefited from this project is 1,000, comprising 2,511 females and 2,530 males. Additionally, 1,712 students benefited from the solar lamps.
+1,000 HH gained access to solar lighting.
+</t>
+  </si>
+  <si>
+    <t>KOICA</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Action Opportunities</t>
+  </si>
+  <si>
+    <t>NDC Support</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of local operators for maintancence </t>
+  </si>
+  <si>
+    <t>30 local operators trained on managing solar water pump systems, including 7 female operators.</t>
+  </si>
+  <si>
+    <t>Water Services</t>
+  </si>
+  <si>
+    <t>Number of HH accessed to water services powered by solar pump</t>
+  </si>
+  <si>
+    <t>Solar Water Pump System: 773 Households or 4,321 individuals (2,148 females and 2,173 males) benefited from this water system.
+- 773 HH gained access to clean water through Solar Water Pump System.</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>3E4Women</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00145070</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>Number of women-owned enterprises with renewable energy system installed</t>
+  </si>
+  <si>
+    <t>Joint SDG Fund</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Financing Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Transformation </t>
+  </si>
+  <si>
+    <t>https://www.undp.org/timor-leste/projects/green-transformation-project</t>
+  </si>
+  <si>
+    <t>Number of people benefited from solar lights and improved cooking stoves</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A total of 5,000 individuals (1,000 HH, with an average of 5 people per household) benefited from solar lights and improved cooking stoves.
+1000 lightings and improved cooking stoves</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Just</t>
+  </si>
+  <si>
+    <t>Health Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of people who benefited from solarized health facilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ Solarized the National Warehouse for Medicines and Medical Equipment (INFPM) and 2 community health posts, providing solar electricity access to an estimated 750,000 people in Timor-Leste.
+</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of people who benefited from solarization of ICT labs in 15 public secondary/vocation schools </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Solarized ICT labs in 15 public secondary/vocational schools, benefiting an estimated 9,000 students.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments </t>
+  </si>
+  <si>
     <t>SEH Taxonomy</t>
   </si>
   <si>
-    <t>RISE Taxonomy</t>
-  </si>
-  <si>
-    <t>Flagship</t>
-  </si>
-  <si>
-    <t>Indirect Category</t>
-  </si>
-  <si>
-    <t>Indirect Taxonomy</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
-    <t>Policy Population</t>
-  </si>
-  <si>
-    <t>The ACCESS project</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00126532</t>
-  </si>
-  <si>
-    <t>Energy Infrastructure Services</t>
-  </si>
-  <si>
     <t>Number of rural HH accessed to solar lightings</t>
   </si>
   <si>
-    <t>1000 HH</t>
-  </si>
-  <si>
     <t>Total number of people benefitted from this project is 5,341 people (female: 2,511 and male: 2,830). In addition number of students benefitted from the project (1,712 people)</t>
   </si>
   <si>
-    <t>KOICA</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Education Services</t>
-  </si>
-  <si>
-    <t>Number of students benefitted</t>
-  </si>
-  <si>
-    <t>Water Services</t>
-  </si>
-  <si>
-    <t>Number of HH accessed to water services powered by solar pump</t>
-  </si>
-  <si>
     <t>593 HH</t>
   </si>
   <si>
@@ -153,43 +270,22 @@
     <t>Energy Efficiency</t>
   </si>
   <si>
-    <t>3E4Women</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00145070</t>
-  </si>
-  <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
-    <t>Number of women-owned enterprises with renewable energy system installed</t>
-  </si>
-  <si>
     <t>100 women-owned enterprises were provieded with electricity access through renewable energy fund</t>
   </si>
   <si>
-    <t>Joint SDG Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green Transformation </t>
-  </si>
-  <si>
     <t>Clean Cooking</t>
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves</t>
+  </si>
+  <si>
+    <t>10600 HH</t>
   </si>
   <si>
     <t>Target beneficiaries benefiting from solar lights and improved cooking stoves is 10,600 people
 1000 lightings and improved cooking stoves</t>
   </si>
   <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Health Services</t>
-  </si>
-  <si>
     <t>Solarization of national warehouse for medicines and medical equipment (SAMES) and 2 community health centers. Estimated beneficiaries</t>
   </si>
   <si>
@@ -197,9 +293,6 @@
 Solarization of national warehouse for medicines and medical equipment (SAMES) and 2 community health centers. Estimated beneficiaries (650,000 people)</t>
   </si>
   <si>
-    <t>Renewable Energy</t>
-  </si>
-  <si>
     <t>Solarization of ICT labs in 15 public secondary/vocation schools with estimated beneficiaries (18,060 people)</t>
   </si>
   <si>
@@ -207,15 +300,6 @@
 3 ICT schools solarized  </t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments </t>
-  </si>
-  <si>
-    <t>10600 HH</t>
-  </si>
-  <si>
     <t>Can you provide information on this project?  Please note that the target number should reflect an estimate of the number of beneficiaries reached by the project. Details can be explained in the note</t>
   </si>
   <si>
@@ -307,9 +391,6 @@
   </si>
   <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
   </si>
   <si>
     <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
@@ -346,10 +427,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,8 +493,21 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +517,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE497"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +689,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -717,36 +819,185 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1077,416 +1328,667 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F479CD-277A-444C-9A31-93368D511EC2}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AO11"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" style="8" customWidth="1"/>
-    <col min="9" max="9" width="65.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="55"/>
+    <col min="2" max="3" width="20.7109375" style="55" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="71" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" style="55" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="67" customWidth="1"/>
+    <col min="9" max="9" width="65.5703125" style="55" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="55"/>
+    <col min="11" max="11" width="12.28515625" style="55" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="61" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="55" customWidth="1"/>
+    <col min="16" max="16" width="24.7109375" style="55" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" style="55" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" style="55" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="47.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:41" ht="47.25" customHeight="1">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="50" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="52" t="s">
+      <c r="R1" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="53" t="s">
+      <c r="S1" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="52" t="s">
+      <c r="T1" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="53" t="s">
+      <c r="U1" s="54" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="4" customFormat="1" ht="60.75">
-      <c r="A2" s="37">
+    <row r="2" spans="1:41" s="61" customFormat="1" ht="84" customHeight="1">
+      <c r="A2" s="84">
         <v>126532</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="35">
-        <v>2700742</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="87">
+        <v>2970297</v>
+      </c>
+      <c r="E2" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="18">
-        <v>0</v>
-      </c>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="22">
-        <v>0.47</v>
-      </c>
-      <c r="L2" s="54" t="s">
+      <c r="K2" s="80">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="47"/>
-      <c r="N2" s="30" t="s">
+      <c r="M2" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="55"/>
-      <c r="X2" s="19" t="s">
+      <c r="N2" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="O2" s="58" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" s="4" customFormat="1" ht="45.75">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="17" t="s">
+      <c r="P2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="Q2" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18">
-        <v>1712</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="54" t="s">
+      <c r="R2" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="54"/>
+    </row>
+    <row r="3" spans="1:41" s="61" customFormat="1" ht="33.75" customHeight="1">
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62">
+        <v>30</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="57"/>
+      <c r="L3" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="47"/>
-      <c r="N3" s="30" t="s">
+      <c r="M3" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="55"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-    </row>
-    <row r="4" spans="1:25" s="4" customFormat="1" ht="60.75">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="17" t="s">
+      <c r="N3" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="62"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="78"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="58"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="58"/>
+      <c r="AK3" s="58"/>
+      <c r="AL3" s="58"/>
+      <c r="AM3" s="60"/>
+      <c r="AN3" s="58"/>
+      <c r="AO3" s="60"/>
+    </row>
+    <row r="4" spans="1:41" s="61" customFormat="1" ht="60.75">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="62"/>
+      <c r="H4" s="73">
+        <v>4321</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="80">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="62"/>
+      <c r="AB4" s="62"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="57"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="58"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="60"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="60"/>
+    </row>
+    <row r="5" spans="1:41" s="61" customFormat="1" ht="78" customHeight="1">
+      <c r="A5" s="75">
+        <v>145070</v>
+      </c>
+      <c r="B5" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="82">
+        <v>280000</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83">
+        <v>100</v>
+      </c>
+      <c r="I5" s="56"/>
+      <c r="J5" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="57">
+        <v>1</v>
+      </c>
+      <c r="L5" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="R5" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" s="86"/>
+      <c r="V5" s="86"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="89"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="62"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="57"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="58"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="58"/>
+      <c r="AJ5" s="58"/>
+      <c r="AK5" s="58"/>
+      <c r="AL5" s="58"/>
+      <c r="AM5" s="60"/>
+      <c r="AN5" s="58"/>
+      <c r="AO5" s="60"/>
+    </row>
+    <row r="6" spans="1:41" s="61" customFormat="1" ht="60.75">
+      <c r="A6" s="84">
+        <v>1000417</v>
+      </c>
+      <c r="B6" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="96">
+        <v>5781240</v>
+      </c>
+      <c r="E6" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F6" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="84" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="79">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18" t="s">
+      <c r="T6" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="54" t="s">
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="77"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="62"/>
+      <c r="AB6" s="62"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="58"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="58"/>
+      <c r="AJ6" s="58"/>
+      <c r="AK6" s="58"/>
+      <c r="AL6" s="58"/>
+      <c r="AM6" s="60"/>
+      <c r="AN6" s="58"/>
+      <c r="AO6" s="60"/>
+    </row>
+    <row r="7" spans="1:41" s="61" customFormat="1" ht="76.5">
+      <c r="A7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="62"/>
+      <c r="H7" s="70">
+        <v>750000</v>
+      </c>
+      <c r="I7" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="85"/>
+      <c r="K7" s="79">
+        <v>0.4</v>
+      </c>
+      <c r="L7" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="47"/>
-      <c r="N4" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="55"/>
-      <c r="X4" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y4" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" s="4" customFormat="1" ht="78" customHeight="1">
-      <c r="A5" s="33">
-        <v>145070</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16">
-        <v>129875</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0</v>
-      </c>
-      <c r="H5" s="16">
-        <v>100</v>
-      </c>
-      <c r="I5" s="19" t="s">
+      <c r="M7" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="20">
-        <v>1</v>
-      </c>
-      <c r="L5" s="54" t="s">
+      <c r="O7" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="84"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="62"/>
+      <c r="AB7" s="62"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="84"/>
+      <c r="AE7" s="59"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="58"/>
+      <c r="AH7" s="59"/>
+      <c r="AI7" s="58"/>
+      <c r="AJ7" s="58"/>
+      <c r="AK7" s="58"/>
+      <c r="AL7" s="58"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="58"/>
+      <c r="AO7" s="60"/>
+    </row>
+    <row r="8" spans="1:41" s="61" customFormat="1" ht="91.5">
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="62"/>
+      <c r="H8" s="70">
+        <v>9000</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="86"/>
+      <c r="K8" s="79">
+        <v>0.4</v>
+      </c>
+      <c r="L8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="47"/>
-      <c r="N5" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="55"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
-    </row>
-    <row r="6" spans="1:25" s="4" customFormat="1" ht="60.75">
-      <c r="A6" s="42">
-        <v>1000417</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="35">
-        <v>700000</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0</v>
-      </c>
-      <c r="H6" s="16">
-        <v>10600</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="47"/>
-      <c r="N6" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="55"/>
-      <c r="X6" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y6" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" s="4" customFormat="1" ht="121.5">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="35">
-        <v>1000000</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0</v>
-      </c>
-      <c r="H7" s="19">
-        <v>650000</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="47"/>
-      <c r="N7" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="55"/>
-      <c r="X7" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" s="4" customFormat="1" ht="91.5">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="35">
-        <v>2000000</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="19">
-        <v>18060</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="47"/>
-      <c r="N8" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="55"/>
-      <c r="X8" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y8" s="19" t="s">
-        <v>53</v>
-      </c>
+      <c r="M8" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T8" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="100"/>
+      <c r="X8" s="69"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="64"/>
+      <c r="AA8" s="62"/>
+      <c r="AB8" s="70"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="59"/>
+      <c r="AF8" s="47"/>
+      <c r="AG8" s="58"/>
+      <c r="AH8" s="59"/>
+      <c r="AI8" s="58"/>
+      <c r="AJ8" s="58"/>
+      <c r="AK8" s="58"/>
+      <c r="AL8" s="58"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="58"/>
+      <c r="AO8" s="60"/>
+    </row>
+    <row r="9" spans="1:41" ht="15">
+      <c r="U9" s="86"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="101"/>
+      <c r="X9" s="69"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="72"/>
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="59"/>
+      <c r="AF9" s="47"/>
+      <c r="AG9" s="58"/>
+      <c r="AH9" s="59"/>
+      <c r="AI9" s="58"/>
+      <c r="AJ9" s="58"/>
+      <c r="AK9" s="58"/>
+      <c r="AL9" s="58"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="58"/>
+      <c r="AO9" s="60"/>
+    </row>
+    <row r="10" spans="1:41" ht="15">
+      <c r="X10" s="71"/>
+      <c r="AA10" s="67"/>
+      <c r="AB10" s="67"/>
+      <c r="AG10" s="61"/>
+    </row>
+    <row r="11" spans="1:41" ht="15">
+      <c r="X11" s="71"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AG11" s="61"/>
     </row>
   </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="X3:X5"/>
+    <mergeCell ref="W3:W5"/>
+    <mergeCell ref="V3:V5"/>
+    <mergeCell ref="U3:U5"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+  </mergeCells>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{7A5099D1-2ED5-43E4-AD13-261638184DF9}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
@@ -1497,7 +1999,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y8" xr:uid="{5BEEAE34-0BCA-4954-A953-F33D3CEC6CD0}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X8 N2:N8" xr:uid="{E8931478-6827-48AC-B5DC-292C1313AC0D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N8 X2:X8" xr:uid="{E8931478-6827-48AC-B5DC-292C1313AC0D}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{BECE492C-710C-49E8-9E3C-10BDCAD51DB5}">
@@ -1522,6 +2024,7 @@
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{779FF747-E687-4012-AE8E-69AFE9D31B33}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{33F8B1CB-D415-4A02-B636-DAE94AE482E9}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{7AC2F46B-FDB9-476B-A50F-9CD4067D20F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1548,7 +2051,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09FFFD-BF9A-4603-B1BD-9865A24B4529}">
   <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
@@ -1598,16 +2101,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="N1" s="28" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="P1" s="28" t="s">
         <v>14</v>
@@ -1622,7 +2125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="4" customFormat="1" ht="91.5">
+    <row r="2" spans="1:19" s="4" customFormat="1" ht="43.5">
       <c r="A2" s="37">
         <v>126532</v>
       </c>
@@ -1636,10 +2139,10 @@
         <v>2700742</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="G2" s="18">
         <v>0</v>
@@ -1648,7 +2151,7 @@
         <v>25</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J2" s="19" t="s">
         <v>27</v>
@@ -1660,32 +2163,32 @@
       <c r="M2" s="10"/>
       <c r="N2" s="19"/>
       <c r="O2" s="19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P2" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="19"/>
       <c r="R2" s="19"/>
       <c r="S2" s="19"/>
     </row>
-    <row r="3" spans="1:19" s="4" customFormat="1" ht="60.75">
+    <row r="3" spans="1:19" s="4" customFormat="1" ht="57.95">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
       <c r="C3" s="40"/>
       <c r="D3" s="35"/>
       <c r="E3" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>27</v>
@@ -1695,10 +2198,10 @@
       <c r="M3" s="10"/>
       <c r="N3" s="19"/>
       <c r="O3" s="19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="19"/>
       <c r="R3" s="19"/>
@@ -1709,19 +2212,19 @@
         <v>145070</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D4" s="16">
         <v>129875</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G4" s="16">
         <v>0</v>
@@ -1730,10 +2233,10 @@
         <v>100</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K4" s="20">
         <v>1</v>
@@ -1752,45 +2255,45 @@
         <v>1000417</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C5" s="32"/>
       <c r="D5" s="35">
         <v>700000</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G5" s="16">
         <v>0</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K5" s="30"/>
       <c r="L5" s="21"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
       <c r="O5" s="19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="19"/>
       <c r="R5" s="19"/>
       <c r="S5" s="19"/>
     </row>
-    <row r="6" spans="1:19" s="4" customFormat="1" ht="137.25">
+    <row r="6" spans="1:19" s="4" customFormat="1" ht="101.45">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="33"/>
@@ -1798,10 +2301,10 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G6" s="16">
         <v>0</v>
@@ -1810,7 +2313,7 @@
         <v>650000</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J6" s="33"/>
       <c r="K6" s="30"/>
@@ -1818,16 +2321,16 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="19"/>
       <c r="R6" s="19"/>
       <c r="S6" s="19"/>
     </row>
-    <row r="7" spans="1:19" s="4" customFormat="1" ht="91.5">
+    <row r="7" spans="1:19" s="4" customFormat="1" ht="87">
       <c r="A7" s="44"/>
       <c r="B7" s="44"/>
       <c r="C7" s="34"/>
@@ -1835,17 +2338,17 @@
         <v>2000000</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="19">
         <v>18060</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="30"/>
@@ -1853,10 +2356,10 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
       <c r="O7" s="19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
@@ -1903,7 +2406,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
@@ -1945,27 +2448,27 @@
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="91.5">
-      <c r="A2" s="58">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="87">
+      <c r="A2" s="107">
         <v>126532</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="108" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="7">
         <v>2700742</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
@@ -1974,40 +2477,40 @@
         <v>1000</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60.75">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="60"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="57.95">
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="109"/>
       <c r="D3" s="7">
         <v>2700742</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13">
         <v>600</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51" customHeight="1">
@@ -2015,52 +2518,52 @@
         <v>145070</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D4" s="7">
         <v>129875</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="56">
+      <c r="A5" s="105">
         <v>1000417</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="57"/>
+      <c r="B5" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="106"/>
       <c r="D5" s="7">
         <v>700000</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G5" s="7">
         <v>0</v>
@@ -2069,24 +2572,24 @@
         <v>1000</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="91.5">
-      <c r="A6" s="56"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
+        <v>86</v>
+      </c>
+      <c r="J5" s="105" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="72.599999999999994">
+      <c r="A6" s="105"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
       <c r="D6" s="7">
         <v>1000000</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
@@ -2095,22 +2598,22 @@
         <v>3</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="1:11" ht="60.75">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
+        <v>88</v>
+      </c>
+      <c r="J6" s="105"/>
+    </row>
+    <row r="7" spans="1:11" ht="57.95">
+      <c r="A7" s="105"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="106"/>
       <c r="D7" s="8">
         <v>2000000</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G7" s="8">
         <v>3</v>
@@ -2119,9 +2622,9 @@
         <v>15</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="56"/>
+        <v>90</v>
+      </c>
+      <c r="J7" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2156,185 +2659,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="45" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>67</v>
+    <row r="2" spans="1:2" ht="43.5">
+      <c r="A2" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="61" t="s">
+      <c r="A3" s="110" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29.1">
+      <c r="A4" s="110" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29.1">
+      <c r="A5" s="110" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="87">
+      <c r="A6" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.5">
+      <c r="A7" s="110" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5">
+      <c r="A8" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.5">
+      <c r="A9" s="110" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29.1">
+      <c r="A10" s="110" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="111" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="29.1">
+      <c r="A11" s="110" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="111" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.5">
+      <c r="A12" s="110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.1">
+      <c r="A13" s="110" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="111" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="110" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29.1">
+      <c r="A15" s="110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="111" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29.1">
+      <c r="A16" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="49" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="62" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="62" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="62" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="62" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="61" t="s">
+      <c r="B16" s="111" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29.1">
+      <c r="A17" s="110" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.1">
+      <c r="A18" s="110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="111" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="72.599999999999994">
+      <c r="A19" s="110" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="111" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29.1">
+      <c r="A20" s="110" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="111" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5">
+      <c r="A21" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="62" t="s">
-        <v>100</v>
+      <c r="B21" s="112" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29.1">
+      <c r="A22" s="110" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="111" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2343,15 +2846,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2362,9 +2856,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2389,6 +2883,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2468,6 +2963,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2611,14 +3111,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA980070-F43E-4A4D-AE3A-45EBDF1E7F16}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA980070-F43E-4A4D-AE3A-45EBDF1E7F16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC7373F-A1ED-4B1E-9E5D-C1BB32FDC35F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21C7E208-C61E-4AAF-AAB6-F295214DA82E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41ADD-8945-43E3-A344-2BC56A5A4FF6}"/>
 </file>
--- a/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Timor-Leste - Energy Projects.xlsx
@@ -287,7 +287,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -633,17 +633,15 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -666,9 +664,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -749,6 +744,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1309,14 +1344,6 @@
       <c r="AR2" s="54" t="n"/>
     </row>
     <row r="3" ht="33.75" customFormat="1" customHeight="1" s="61">
-      <c r="A3" s="117" t="n"/>
-      <c r="B3" s="117" t="n"/>
-      <c r="C3" s="117" t="n"/>
-      <c r="D3" s="117" t="n"/>
-      <c r="E3" s="117" t="n"/>
-      <c r="F3" s="117" t="n"/>
-      <c r="G3" s="117" t="n"/>
-      <c r="H3" s="117" t="n"/>
       <c r="I3" s="56" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -1380,7 +1407,7 @@
       </c>
       <c r="X3" s="113" t="n"/>
       <c r="Y3" s="113" t="n"/>
-      <c r="Z3" s="118" t="n"/>
+      <c r="Z3" s="117" t="n"/>
       <c r="AA3" s="115" t="n"/>
       <c r="AB3" s="56" t="n"/>
       <c r="AC3" s="56" t="n"/>
@@ -1401,14 +1428,6 @@
       <c r="AR3" s="60" t="n"/>
     </row>
     <row r="4" ht="60.75" customFormat="1" customHeight="1" s="61">
-      <c r="A4" s="119" t="n"/>
-      <c r="B4" s="119" t="n"/>
-      <c r="C4" s="119" t="n"/>
-      <c r="D4" s="119" t="n"/>
-      <c r="E4" s="119" t="n"/>
-      <c r="F4" s="119" t="n"/>
-      <c r="G4" s="119" t="n"/>
-      <c r="H4" s="119" t="n"/>
       <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Water Services</t>
@@ -1454,13 +1473,21 @@
         </is>
       </c>
       <c r="T4" s="58" t="n"/>
-      <c r="U4" s="117" t="n"/>
-      <c r="V4" s="117" t="n"/>
-      <c r="W4" s="117" t="n"/>
-      <c r="X4" s="117" t="n"/>
-      <c r="Y4" s="117" t="n"/>
-      <c r="Z4" s="117" t="n"/>
-      <c r="AA4" s="117" t="n"/>
+      <c r="U4" s="58" t="inlineStr">
+        <is>
+          <t>Renewable Energy</t>
+        </is>
+      </c>
+      <c r="V4" s="60" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="W4" s="58" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
       <c r="AB4" s="56" t="n"/>
       <c r="AC4" s="56" t="n"/>
       <c r="AD4" s="62" t="n"/>
@@ -1480,14 +1507,6 @@
       <c r="AR4" s="60" t="n"/>
     </row>
     <row r="5" ht="78" customFormat="1" customHeight="1" s="61">
-      <c r="A5" s="119" t="n"/>
-      <c r="B5" s="119" t="n"/>
-      <c r="C5" s="119" t="n"/>
-      <c r="D5" s="119" t="n"/>
-      <c r="E5" s="119" t="n"/>
-      <c r="F5" s="119" t="n"/>
-      <c r="G5" s="119" t="n"/>
-      <c r="H5" s="119" t="n"/>
       <c r="I5" s="56" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1498,15 +1517,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K5" s="62" t="n">
+      <c r="K5" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="120" t="n"/>
-      <c r="M5" s="121" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L5" s="119" t="n"/>
+      <c r="M5" s="56" t="n"/>
       <c r="N5" s="56" t="n"/>
       <c r="O5" s="80" t="n"/>
       <c r="P5" s="58" t="n"/>
@@ -1514,13 +1529,9 @@
       <c r="R5" s="58" t="n"/>
       <c r="S5" s="58" t="n"/>
       <c r="T5" s="58" t="n"/>
-      <c r="U5" s="119" t="n"/>
-      <c r="V5" s="119" t="n"/>
-      <c r="W5" s="119" t="n"/>
-      <c r="X5" s="119" t="n"/>
-      <c r="Y5" s="117" t="n"/>
-      <c r="Z5" s="117" t="n"/>
-      <c r="AA5" s="117" t="n"/>
+      <c r="U5" s="58" t="n"/>
+      <c r="V5" s="60" t="n"/>
+      <c r="W5" s="58" t="n"/>
       <c r="AB5" s="56" t="n"/>
       <c r="AC5" s="56" t="n"/>
       <c r="AD5" s="62" t="n"/>
@@ -1540,26 +1551,26 @@
       <c r="AR5" s="60" t="n"/>
     </row>
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="61">
-      <c r="A6" s="113" t="n">
+      <c r="A6" s="84" t="n">
         <v>145070</v>
       </c>
-      <c r="B6" s="113" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>3E4Women</t>
         </is>
       </c>
-      <c r="C6" s="125" t="inlineStr">
+      <c r="C6" s="93" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00145070</t>
         </is>
       </c>
-      <c r="D6" s="122" t="n">
+      <c r="D6" s="120" t="n">
         <v>280000</v>
       </c>
-      <c r="E6" s="123" t="n"/>
-      <c r="F6" s="123" t="n"/>
-      <c r="G6" s="123" t="n"/>
-      <c r="H6" s="122" t="inlineStr">
+      <c r="E6" s="121" t="n"/>
+      <c r="F6" s="121" t="n"/>
+      <c r="G6" s="121" t="n"/>
+      <c r="H6" s="120" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -1623,10 +1634,6 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="X6" s="119" t="n"/>
-      <c r="Y6" s="119" t="n"/>
-      <c r="Z6" s="119" t="n"/>
-      <c r="AA6" s="119" t="n"/>
       <c r="AB6" s="56" t="n"/>
       <c r="AC6" s="56" t="n"/>
       <c r="AD6" s="62" t="n"/>
@@ -1646,29 +1653,29 @@
       <c r="AR6" s="60" t="n"/>
     </row>
     <row r="7" ht="76.5" customFormat="1" customHeight="1" s="61">
-      <c r="A7" s="117" t="n"/>
-      <c r="B7" s="117" t="n"/>
-      <c r="C7" s="117" t="n"/>
-      <c r="D7" s="117" t="n"/>
-      <c r="E7" s="122" t="n"/>
-      <c r="F7" s="122" t="n"/>
-      <c r="G7" s="122" t="n"/>
-      <c r="H7" s="122" t="n"/>
+      <c r="A7" s="84" t="n"/>
+      <c r="B7" s="84" t="n"/>
+      <c r="C7" s="93" t="n"/>
+      <c r="D7" s="120" t="n"/>
+      <c r="E7" s="120" t="n"/>
+      <c r="F7" s="120" t="n"/>
+      <c r="G7" s="120" t="n"/>
+      <c r="H7" s="120" t="n"/>
       <c r="I7" s="56" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J7" s="117" t="n"/>
-      <c r="K7" s="83" t="n">
+      <c r="J7" s="56" t="inlineStr">
+        <is>
+          <t>Installed capacity in MW for access/productive-use outputs</t>
+        </is>
+      </c>
+      <c r="K7" s="122" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="124" t="n"/>
-      <c r="M7" s="121" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L7" s="122" t="n"/>
+      <c r="M7" s="56" t="n"/>
       <c r="N7" s="63" t="n"/>
       <c r="O7" s="57" t="n"/>
       <c r="P7" s="58" t="n"/>
@@ -1679,10 +1686,6 @@
       <c r="U7" s="58" t="n"/>
       <c r="V7" s="60" t="n"/>
       <c r="W7" s="58" t="n"/>
-      <c r="X7" s="119" t="n"/>
-      <c r="Y7" s="119" t="n"/>
-      <c r="Z7" s="119" t="n"/>
-      <c r="AA7" s="119" t="n"/>
       <c r="AB7" s="56" t="n"/>
       <c r="AC7" s="56" t="n"/>
       <c r="AD7" s="62" t="n"/>
@@ -1702,20 +1705,40 @@
       <c r="AR7" s="60" t="n"/>
     </row>
     <row r="8" ht="91.5" customFormat="1" customHeight="1" s="61">
-      <c r="A8" s="119" t="n"/>
-      <c r="B8" s="119" t="n"/>
-      <c r="C8" s="119" t="n"/>
-      <c r="D8" s="119" t="n"/>
-      <c r="E8" s="127" t="n"/>
-      <c r="F8" s="127" t="n"/>
-      <c r="G8" s="127" t="n"/>
-      <c r="H8" s="126" t="n"/>
+      <c r="A8" s="113" t="n">
+        <v>1000417</v>
+      </c>
+      <c r="B8" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green Transformation </t>
+        </is>
+      </c>
+      <c r="C8" s="123" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/timor-leste/projects/green-transformation-project</t>
+        </is>
+      </c>
+      <c r="D8" s="124" t="n">
+        <v>5781240</v>
+      </c>
+      <c r="E8" s="125" t="n"/>
+      <c r="F8" s="125" t="n"/>
+      <c r="G8" s="125" t="n"/>
+      <c r="H8" s="124" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
       <c r="I8" s="56" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="J8" s="119" t="n"/>
+      <c r="J8" s="64" t="inlineStr">
+        <is>
+          <t>Number of people benefited from solar lights and improved cooking stoves</t>
+        </is>
+      </c>
       <c r="K8" s="62" t="n"/>
       <c r="L8" s="62" t="n">
         <v>5000</v>
@@ -1755,16 +1778,28 @@
           <t>NDC Support</t>
         </is>
       </c>
-      <c r="U8" s="117" t="n"/>
-      <c r="V8" s="117" t="n"/>
-      <c r="W8" s="117" t="n"/>
+      <c r="U8" s="58" t="inlineStr">
+        <is>
+          <t>Renewable Energy</t>
+        </is>
+      </c>
+      <c r="V8" s="60" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="W8" s="58" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
       <c r="X8" s="84" t="n"/>
       <c r="Y8" s="84" t="n"/>
       <c r="Z8" s="99" t="n"/>
       <c r="AA8" s="70" t="n"/>
       <c r="AB8" s="56" t="n"/>
       <c r="AC8" s="56" t="n"/>
-      <c r="AD8" s="117" t="n"/>
+      <c r="AD8" s="62" t="n"/>
       <c r="AE8" s="62" t="n"/>
       <c r="AF8" s="56" t="n"/>
       <c r="AG8" s="63" t="n"/>
@@ -1781,14 +1816,6 @@
       <c r="AR8" s="60" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="117" t="n"/>
-      <c r="B9" s="117" t="n"/>
-      <c r="C9" s="117" t="n"/>
-      <c r="D9" s="117" t="n"/>
-      <c r="E9" s="117" t="n"/>
-      <c r="F9" s="117" t="n"/>
-      <c r="G9" s="117" t="n"/>
-      <c r="H9" s="117" t="n"/>
       <c r="I9" s="56" t="inlineStr">
         <is>
           <t>Health Services</t>
@@ -1810,7 +1837,6 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="117" t="n"/>
       <c r="O9" s="79" t="n">
         <v>0.4</v>
       </c>
@@ -1835,20 +1861,32 @@
           <t>NDC Support</t>
         </is>
       </c>
-      <c r="U9" s="119" t="n"/>
-      <c r="V9" s="119" t="n"/>
-      <c r="W9" s="119" t="n"/>
+      <c r="U9" s="58" t="inlineStr">
+        <is>
+          <t>Renewable Energy</t>
+        </is>
+      </c>
+      <c r="V9" s="60" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="W9" s="58" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
       <c r="X9" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
       <c r="Y9" s="113" t="n"/>
-      <c r="Z9" s="128" t="n"/>
+      <c r="Z9" s="126" t="n"/>
       <c r="AA9" s="69" t="n"/>
       <c r="AB9" s="56" t="n"/>
       <c r="AC9" s="64" t="n"/>
-      <c r="AD9" s="119" t="n"/>
+      <c r="AD9" s="62" t="n"/>
       <c r="AE9" s="62" t="n"/>
       <c r="AF9" s="65" t="n"/>
       <c r="AG9" s="113" t="n"/>
@@ -1865,14 +1903,6 @@
       <c r="AR9" s="60" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="119" t="n"/>
-      <c r="B10" s="119" t="n"/>
-      <c r="C10" s="119" t="n"/>
-      <c r="D10" s="119" t="n"/>
-      <c r="E10" s="119" t="n"/>
-      <c r="F10" s="119" t="n"/>
-      <c r="G10" s="119" t="n"/>
-      <c r="H10" s="119" t="n"/>
       <c r="I10" s="56" t="inlineStr">
         <is>
           <t>Education Services</t>
@@ -1893,7 +1923,6 @@
 Solarized ICT labs in 15 public secondary/vocational schools, benefiting an estimated 9,000 students.</t>
         </is>
       </c>
-      <c r="N10" s="119" t="n"/>
       <c r="O10" s="79" t="n">
         <v>0.4</v>
       </c>
@@ -1933,16 +1962,12 @@
           <t>National</t>
         </is>
       </c>
-      <c r="X10" s="117" t="n"/>
-      <c r="Y10" s="117" t="n"/>
-      <c r="Z10" s="117" t="n"/>
       <c r="AA10" s="69" t="n"/>
       <c r="AB10" s="56" t="n"/>
       <c r="AC10" s="64" t="n"/>
       <c r="AD10" s="62" t="n"/>
       <c r="AE10" s="70" t="n"/>
       <c r="AF10" s="65" t="n"/>
-      <c r="AG10" s="117" t="n"/>
       <c r="AH10" s="59" t="n"/>
       <c r="AI10" s="47" t="n"/>
       <c r="AJ10" s="58" t="n"/>
@@ -1956,14 +1981,6 @@
       <c r="AR10" s="60" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="119" t="n"/>
-      <c r="B11" s="119" t="n"/>
-      <c r="C11" s="119" t="n"/>
-      <c r="D11" s="119" t="n"/>
-      <c r="E11" s="119" t="n"/>
-      <c r="F11" s="119" t="n"/>
-      <c r="G11" s="119" t="n"/>
-      <c r="H11" s="119" t="n"/>
       <c r="I11" s="56" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1974,16 +1991,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="62" t="n">
+      <c r="K11" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="129" t="n"/>
-      <c r="M11" s="130" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N11" s="119" t="n"/>
+      <c r="L11" s="127" t="n"/>
+      <c r="M11" s="65" t="n"/>
       <c r="O11" s="79" t="n"/>
       <c r="P11" s="58" t="n"/>
       <c r="Q11" s="59" t="n"/>
@@ -1993,16 +2005,12 @@
       <c r="U11" s="58" t="n"/>
       <c r="V11" s="60" t="n"/>
       <c r="W11" s="58" t="n"/>
-      <c r="X11" s="117" t="n"/>
-      <c r="Y11" s="117" t="n"/>
-      <c r="Z11" s="117" t="n"/>
       <c r="AA11" s="69" t="n"/>
       <c r="AB11" s="56" t="n"/>
       <c r="AC11" s="64" t="n"/>
       <c r="AD11" s="62" t="n"/>
       <c r="AE11" s="70" t="n"/>
       <c r="AF11" s="65" t="n"/>
-      <c r="AG11" s="117" t="n"/>
       <c r="AH11" s="59" t="n"/>
       <c r="AI11" s="47" t="n"/>
       <c r="AJ11" s="58" t="n"/>
@@ -2016,16 +2024,12 @@
       <c r="AR11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="X12" s="119" t="n"/>
-      <c r="Y12" s="119" t="n"/>
-      <c r="Z12" s="119" t="n"/>
       <c r="AA12" s="69" t="n"/>
       <c r="AB12" s="56" t="n"/>
       <c r="AC12" s="66" t="n"/>
       <c r="AD12" s="62" t="n"/>
       <c r="AE12" s="70" t="n"/>
       <c r="AF12" s="72" t="n"/>
-      <c r="AG12" s="119" t="n"/>
       <c r="AH12" s="59" t="n"/>
       <c r="AI12" s="47" t="n"/>
       <c r="AJ12" s="58" t="n"/>
@@ -2051,26 +2055,7 @@
       <c r="AJ14" s="61" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="X3:X5"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="W3:W5"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="U3:U5"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="V3:V5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="AD7:AD9"/>
-  </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="Q2:Q8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2104,18 +2089,13 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2919,12 +2899,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="131" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="131" t="inlineStr">
+      <c r="B1" s="128" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
